--- a/Proyecto/output/INDICADORES_NORMALIZADOS.xlsx
+++ b/Proyecto/output/INDICADORES_NORMALIZADOS.xlsx
@@ -1,21 +1,68 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d11b7e7c31b62c39/Escritorio/PROGRAMACIÓN II/programa-II/Proyecto/output/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_10D65FCD8F79A8D366075C52F37BD2723A45FF1D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77147B42-14B7-4476-9D1A-41E4E072186E}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+  <si>
+    <t>depto</t>
+  </si>
+  <si>
+    <t>var_uso_intern</t>
+  </si>
+  <si>
+    <t>var_uso_intern_mujeres</t>
+  </si>
+  <si>
+    <t>var_uso_acceso_tel_mov</t>
+  </si>
+  <si>
+    <t>pct_rural</t>
+  </si>
+  <si>
+    <t>propor_hogares_internet</t>
+  </si>
+  <si>
+    <t>propor_hogares_computadora</t>
+  </si>
+  <si>
+    <t>rb_por_100k</t>
+  </si>
+  <si>
+    <t>lineas_por_1k</t>
+  </si>
+  <si>
+    <t>pib_per_capita</t>
+  </si>
+  <si>
+    <t>IDT_media</t>
+  </si>
+  <si>
+    <t>IDT_geo</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +110,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +162,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +196,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +231,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,90 +407,69 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>depto</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>var_uso_intern</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>var_uso_intern_mujeres</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>var_uso_acceso_tel_mov</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>pct_rural</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>propor_hogares_internet</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>propor_hogares_computadora</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>rb_por_100k</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>lineas_por_1k</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>pib_per_capita</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>IDT_media</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>IDT_geo</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>67.40506329113923</v>
+        <v>67.405063291139228</v>
       </c>
       <c r="C2">
-        <v>38.5222702219574</v>
+        <v>38.522270221957399</v>
       </c>
       <c r="D2">
-        <v>72.97811607992388</v>
+        <v>72.978116079923879</v>
       </c>
       <c r="E2">
         <v>100</v>
       </c>
       <c r="F2">
-        <v>53.76123639804447</v>
+        <v>53.761236398044467</v>
       </c>
       <c r="G2">
         <v>84.19052444894858</v>
@@ -442,77 +478,77 @@
         <v>100</v>
       </c>
       <c r="I2">
-        <v>99.98991172761666</v>
+        <v>99.989911727616658</v>
       </c>
       <c r="J2">
-        <v>99.99974278816369</v>
+        <v>99.999742788163687</v>
       </c>
       <c r="K2">
-        <v>79.64965166175489</v>
+        <v>79.649651661754888</v>
       </c>
       <c r="L2">
-        <v>76.46221087996028</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>76.462210879960281</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>48.98734177215189</v>
+        <v>48.987341772151893</v>
       </c>
       <c r="C3">
-        <v>27.06688514821987</v>
+        <v>27.066885148219871</v>
       </c>
       <c r="D3">
-        <v>52.65461465271171</v>
+        <v>52.654614652711707</v>
       </c>
       <c r="E3">
-        <v>59.90205081114173</v>
+        <v>59.902050811141727</v>
       </c>
       <c r="F3">
-        <v>20.02838668979656</v>
+        <v>20.028386689796559</v>
       </c>
       <c r="G3">
-        <v>25.56371928046618</v>
+        <v>25.563719280466181</v>
       </c>
       <c r="H3">
         <v>100</v>
       </c>
       <c r="I3">
-        <v>9.979823455233291</v>
+        <v>9.9798234552332907</v>
       </c>
       <c r="J3">
-        <v>32.1357398379486</v>
+        <v>32.135739837948599</v>
       </c>
       <c r="K3">
-        <v>41.81317351640777</v>
+        <v>41.813173516407772</v>
       </c>
       <c r="L3">
-        <v>35.14062435144429</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>35.140624351444288</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>53.0379746835443</v>
+        <v>53.037974683544299</v>
       </c>
       <c r="C4">
         <v>26.30716520184717</v>
       </c>
       <c r="D4">
-        <v>66.98382492863938</v>
+        <v>66.983824928639379</v>
       </c>
       <c r="E4">
         <v>100</v>
       </c>
       <c r="F4">
-        <v>20.23340167166062</v>
+        <v>20.233401671660619</v>
       </c>
       <c r="G4">
-        <v>67.01292120597923</v>
+        <v>67.012921205979225</v>
       </c>
       <c r="H4">
         <v>100</v>
@@ -521,68 +557,68 @@
         <v>11.65447667087011</v>
       </c>
       <c r="J4">
-        <v>38.89246539518339</v>
+        <v>38.892465395183393</v>
       </c>
       <c r="K4">
-        <v>53.79135886196936</v>
+        <v>53.791358861969357</v>
       </c>
       <c r="L4">
-        <v>44.56489904785656</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>44.564899047856557</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>36.39240506329114</v>
+        <v>36.392405063291143</v>
       </c>
       <c r="C5">
-        <v>20.76567853418739</v>
+        <v>20.765678534187391</v>
       </c>
       <c r="D5">
-        <v>47.34538534728829</v>
+        <v>47.345385347288293</v>
       </c>
       <c r="E5">
-        <v>50.93357820630548</v>
+        <v>50.933578206305476</v>
       </c>
       <c r="F5">
-        <v>22.85128528623246</v>
+        <v>22.851285286232461</v>
       </c>
       <c r="G5">
         <v>29.03470990625792</v>
       </c>
       <c r="H5">
-        <v>90.42136771816715</v>
+        <v>90.421367718167147</v>
       </c>
       <c r="I5">
-        <v>2.62547288776797</v>
+        <v>2.6254728877679701</v>
       </c>
       <c r="J5">
-        <v>12.40541980730186</v>
+        <v>12.405419807301859</v>
       </c>
       <c r="K5">
         <v>34.75281141742218</v>
       </c>
       <c r="L5">
-        <v>25.65988568355099</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>25.659885683550989</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>54.03481012658229</v>
+        <v>54.034810126582293</v>
       </c>
       <c r="C6">
-        <v>30.58245195888574</v>
+        <v>30.582451958885741</v>
       </c>
       <c r="D6">
-        <v>54.10085632730733</v>
+        <v>54.100856327307334</v>
       </c>
       <c r="E6">
-        <v>62.0599938781757</v>
+        <v>62.059993878175703</v>
       </c>
       <c r="F6">
         <v>21.38463964674342</v>
@@ -594,19 +630,19 @@
         <v>100</v>
       </c>
       <c r="I6">
-        <v>5.457755359394704</v>
+        <v>5.4577553593947039</v>
       </c>
       <c r="J6">
         <v>71.86871015695499</v>
       </c>
       <c r="K6">
-        <v>46.7551710523073</v>
+        <v>46.755171052307297</v>
       </c>
       <c r="L6">
-        <v>36.86528831857206</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>36.865288318572063</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -614,37 +650,37 @@
         <v>48.87658227848101</v>
       </c>
       <c r="C7">
-        <v>25.48785937732758</v>
+        <v>25.487859377327581</v>
       </c>
       <c r="D7">
-        <v>52.29305423406279</v>
+        <v>52.293054234062787</v>
       </c>
       <c r="E7">
-        <v>44.65870829507194</v>
+        <v>44.658708295071939</v>
       </c>
       <c r="F7">
         <v>23.90790096199337</v>
       </c>
       <c r="G7">
-        <v>8.791487205472512</v>
+        <v>8.7914872054725119</v>
       </c>
       <c r="H7">
         <v>100</v>
       </c>
       <c r="I7">
-        <v>3.32156368221942</v>
+        <v>3.3215636822194199</v>
       </c>
       <c r="J7">
-        <v>24.31069362280685</v>
+        <v>24.310693622806848</v>
       </c>
       <c r="K7">
-        <v>36.84976107304838</v>
+        <v>36.849761073048377</v>
       </c>
       <c r="L7">
-        <v>26.66835968917047</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>26.668359689170469</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -652,10 +688,10 @@
         <v>34.87341772151899</v>
       </c>
       <c r="C8">
-        <v>19.29092805005214</v>
+        <v>19.290928050052141</v>
       </c>
       <c r="D8">
-        <v>42.72121788772596</v>
+        <v>42.721217887725963</v>
       </c>
       <c r="E8">
         <v>73.82920110192839</v>
@@ -664,25 +700,25 @@
         <v>28.79671976029017</v>
       </c>
       <c r="G8">
-        <v>34.43121357993413</v>
+        <v>34.431213579934131</v>
       </c>
       <c r="H8">
-        <v>96.91457517844808</v>
+        <v>96.914575178448075</v>
       </c>
       <c r="I8">
-        <v>3.003783102143757</v>
+        <v>3.0037831021437569</v>
       </c>
       <c r="J8">
         <v>15.46238058392113</v>
       </c>
       <c r="K8">
-        <v>38.81371521844031</v>
+        <v>38.813715218440308</v>
       </c>
       <c r="L8">
         <v>28.61102576418758</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -693,92 +729,92 @@
         <v>17.04156115000745</v>
       </c>
       <c r="D9">
-        <v>33.60608943862987</v>
+        <v>33.606089438629873</v>
       </c>
       <c r="E9">
-        <v>50.7040097949189</v>
+        <v>50.704009794918903</v>
       </c>
       <c r="F9">
         <v>22.44125532250434</v>
       </c>
       <c r="G9">
-        <v>25.69039777045858</v>
+        <v>25.690397770458581</v>
       </c>
       <c r="H9">
-        <v>72.16209993092332</v>
+        <v>72.162099930923318</v>
       </c>
       <c r="I9">
-        <v>4.158890290037832</v>
+        <v>4.1588902900378324</v>
       </c>
       <c r="J9">
-        <v>18.80938679167865</v>
+        <v>18.809386791678651</v>
       </c>
       <c r="K9">
-        <v>30.47043818374621</v>
+        <v>30.470438183746211</v>
       </c>
       <c r="L9">
-        <v>24.72245877032839</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>24.722458770328391</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
-        <v>48.8132911392405</v>
+        <v>48.813291139240498</v>
       </c>
       <c r="C10">
-        <v>28.33308505884106</v>
+        <v>28.333085058841061</v>
       </c>
       <c r="D10">
-        <v>52.25499524262607</v>
+        <v>52.254995242626073</v>
       </c>
       <c r="E10">
         <v>60.88154269972452</v>
       </c>
       <c r="F10">
-        <v>36.19302949061662</v>
+        <v>36.193029490616617</v>
       </c>
       <c r="G10">
-        <v>41.37319483151761</v>
+        <v>41.373194831517608</v>
       </c>
       <c r="H10">
         <v>100</v>
       </c>
       <c r="I10">
-        <v>36.82723833543506</v>
+        <v>36.827238335435062</v>
       </c>
       <c r="J10">
-        <v>43.90377994851904</v>
+        <v>43.903779948519038</v>
       </c>
       <c r="K10">
-        <v>49.84223963850228</v>
+        <v>49.842239638502278</v>
       </c>
       <c r="L10">
-        <v>47.0441701747612</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>47.044170174761199</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>39.95253164556961</v>
+        <v>39.952531645569607</v>
       </c>
       <c r="C11">
-        <v>21.10829733353195</v>
+        <v>21.108297333531951</v>
       </c>
       <c r="D11">
-        <v>40.9324452901998</v>
+        <v>40.932445290199801</v>
       </c>
       <c r="E11">
-        <v>50.27548209366392</v>
+        <v>50.275482093663918</v>
       </c>
       <c r="F11">
         <v>15.07648635861851</v>
       </c>
       <c r="G11">
-        <v>17.1015961489739</v>
+        <v>17.101596148973901</v>
       </c>
       <c r="H11">
         <v>100</v>
@@ -790,65 +826,65 @@
         <v>23.05019418240245</v>
       </c>
       <c r="K11">
-        <v>34.57995617360199</v>
+        <v>34.579956173601992</v>
       </c>
       <c r="L11">
         <v>25.84104472090938</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12">
-        <v>39.84177215189872</v>
+        <v>39.841772151898716</v>
       </c>
       <c r="C12">
-        <v>21.83822434083122</v>
+        <v>21.838224340831221</v>
       </c>
       <c r="D12">
         <v>46.52711703139866</v>
       </c>
       <c r="E12">
-        <v>55.29537802265077</v>
+        <v>55.295378022650773</v>
       </c>
       <c r="F12">
-        <v>16.66929506387005</v>
+        <v>16.669295063870049</v>
       </c>
       <c r="G12">
-        <v>19.07778059285534</v>
+        <v>19.077780592855341</v>
       </c>
       <c r="H12">
         <v>100</v>
       </c>
       <c r="I12">
-        <v>4.877679697351827</v>
+        <v>4.8776796973518266</v>
       </c>
       <c r="J12">
-        <v>30.88813631281078</v>
+        <v>30.888136312810779</v>
       </c>
       <c r="K12">
-        <v>37.22393146818526</v>
+        <v>37.223931468185263</v>
       </c>
       <c r="L12">
-        <v>28.84844089542496</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>28.848440895424961</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
-        <v>35.31645569620252</v>
+        <v>35.316455696202517</v>
       </c>
       <c r="C13">
-        <v>22.07656785341874</v>
+        <v>22.076567853418741</v>
       </c>
       <c r="D13">
-        <v>37.98287345385347</v>
+        <v>37.982873453853472</v>
       </c>
       <c r="E13">
-        <v>12.51913070094889</v>
+        <v>12.519130700948891</v>
       </c>
       <c r="F13">
         <v>14.06718183251853</v>
@@ -863,36 +899,36 @@
         <v>2.179066834804539</v>
       </c>
       <c r="J13">
-        <v>26.04660437132806</v>
+        <v>26.046604371328058</v>
       </c>
       <c r="K13">
         <v>29.91277665999257</v>
       </c>
       <c r="L13">
-        <v>21.02097873933013</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>21.020978739330129</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
-        <v>29.88924050632911</v>
+        <v>29.889240506329109</v>
       </c>
       <c r="C14">
-        <v>18.65037985997319</v>
+        <v>18.650379859973189</v>
       </c>
       <c r="D14">
-        <v>35.2045670789724</v>
+        <v>35.204567078972403</v>
       </c>
       <c r="E14">
         <v>29.10927456382003</v>
       </c>
       <c r="F14">
-        <v>20.04415707301687</v>
+        <v>20.044157073016869</v>
       </c>
       <c r="G14">
-        <v>22.24474284266532</v>
+        <v>22.244742842665321</v>
       </c>
       <c r="H14">
         <v>100</v>
@@ -910,12 +946,12 @@
         <v>21.22599522731813</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15">
-        <v>21.89873417721519</v>
+        <v>21.898734177215189</v>
       </c>
       <c r="C15">
         <v>14.24102487710412</v>
@@ -927,13 +963,13 @@
         <v>30.93051729415367</v>
       </c>
       <c r="F15">
-        <v>8.973348052357673</v>
+        <v>8.9733480523576734</v>
       </c>
       <c r="G15">
         <v>12.79452748923233</v>
       </c>
       <c r="H15">
-        <v>73.01404559060555</v>
+        <v>73.014045590605548</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -942,33 +978,33 @@
         <v>10.62310026520626</v>
       </c>
       <c r="K15">
-        <v>22.50465566454323</v>
+        <v>22.504655664543229</v>
       </c>
       <c r="L15">
-        <v>3.770805105863815</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>3.7708051058638148</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16">
-        <v>25.31645569620253</v>
+        <v>25.316455696202532</v>
       </c>
       <c r="C16">
         <v>16.69894235066289</v>
       </c>
       <c r="D16">
-        <v>37.79257849666983</v>
+        <v>37.792578496669833</v>
       </c>
       <c r="E16">
-        <v>27.97673706764616</v>
+        <v>27.976737067646159</v>
       </c>
       <c r="F16">
         <v>11.48083898438732</v>
       </c>
       <c r="G16">
-        <v>28.37598175829745</v>
+        <v>28.375981758297449</v>
       </c>
       <c r="H16">
         <v>100</v>
@@ -980,13 +1016,13 @@
         <v>13.55857766418057</v>
       </c>
       <c r="K16">
-        <v>29.18813070342035</v>
+        <v>29.188130703420349</v>
       </c>
       <c r="L16">
-        <v>19.65494972661049</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>19.654949726610489</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -994,25 +1030,25 @@
         <v>12.37341772151899</v>
       </c>
       <c r="C17">
-        <v>6.524653657083272</v>
+        <v>6.5246536570832721</v>
       </c>
       <c r="D17">
-        <v>12.8068506184586</v>
+        <v>12.806850618458601</v>
       </c>
       <c r="E17">
-        <v>21.04377104377104</v>
+        <v>21.043771043771041</v>
       </c>
       <c r="F17">
-        <v>5.283078378804604</v>
+        <v>5.2830783788046043</v>
       </c>
       <c r="G17">
-        <v>9.931593615404106</v>
+        <v>9.9315936154041058</v>
       </c>
       <c r="H17">
-        <v>36.72576559981579</v>
+        <v>36.725765599815787</v>
       </c>
       <c r="I17">
-        <v>0.1361916771752835</v>
+        <v>0.13619167717528349</v>
       </c>
       <c r="J17">
         <v>16.73036592591232</v>
@@ -1021,48 +1057,48 @@
         <v>13.50618758199378</v>
       </c>
       <c r="L17">
-        <v>8.148322751216295</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>8.1483227512162948</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18">
-        <v>45.61708860759494</v>
+        <v>45.617088607594937</v>
       </c>
       <c r="C18">
-        <v>26.24757932370028</v>
+        <v>26.247579323700279</v>
       </c>
       <c r="D18">
-        <v>40.79923882017125</v>
+        <v>40.799238820171247</v>
       </c>
       <c r="E18">
-        <v>31.34374043464953</v>
+        <v>31.343740434649529</v>
       </c>
       <c r="F18">
         <v>21.38463964674342</v>
       </c>
       <c r="G18">
-        <v>26.45046871041298</v>
+        <v>26.450468710412981</v>
       </c>
       <c r="H18">
         <v>100</v>
       </c>
       <c r="I18">
-        <v>2.66078184110971</v>
+        <v>2.6607818411097099</v>
       </c>
       <c r="J18">
-        <v>31.2700862235931</v>
+        <v>31.270086223593101</v>
       </c>
       <c r="K18">
-        <v>36.19706928977502</v>
+        <v>36.197069289775023</v>
       </c>
       <c r="L18">
-        <v>27.64628017108999</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>27.646280171089991</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1073,54 +1109,54 @@
         <v>24.53448532697751</v>
       </c>
       <c r="D19">
-        <v>38.55375832540437</v>
+        <v>38.553758325404367</v>
       </c>
       <c r="E19">
-        <v>31.11417202326294</v>
+        <v>31.114172023262942</v>
       </c>
       <c r="F19">
-        <v>34.03248698943385</v>
+        <v>34.032486989433849</v>
       </c>
       <c r="G19">
-        <v>19.53382315682797</v>
+        <v>19.533823156827971</v>
       </c>
       <c r="H19">
         <v>100</v>
       </c>
       <c r="I19">
-        <v>9.235813366960908</v>
+        <v>9.2358133669609082</v>
       </c>
       <c r="J19">
-        <v>39.82388347283774</v>
+        <v>39.823883472837743</v>
       </c>
       <c r="K19">
-        <v>37.85611166002069</v>
+        <v>37.856111660020687</v>
       </c>
       <c r="L19">
         <v>32.19193316292214</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20">
-        <v>44.09810126582278</v>
+        <v>44.098101265822777</v>
       </c>
       <c r="C20">
-        <v>24.44510650975719</v>
+        <v>24.445106509757188</v>
       </c>
       <c r="D20">
-        <v>46.73644148430065</v>
+        <v>46.736441484300649</v>
       </c>
       <c r="E20">
-        <v>40.43464952555863</v>
+        <v>40.434649525558633</v>
       </c>
       <c r="F20">
         <v>26.7623403248699</v>
       </c>
       <c r="G20">
-        <v>28.55333164428681</v>
+        <v>28.553331644286811</v>
       </c>
       <c r="H20">
         <v>100</v>
@@ -1129,74 +1165,74 @@
         <v>10.48928121059269</v>
       </c>
       <c r="J20">
-        <v>44.22226093496371</v>
+        <v>44.222260934963707</v>
       </c>
       <c r="K20">
-        <v>40.63794587779471</v>
+        <v>40.637945877794706</v>
       </c>
       <c r="L20">
         <v>35.2169758301794</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21">
-        <v>32.34177215189874</v>
+        <v>32.341772151898738</v>
       </c>
       <c r="C21">
-        <v>18.41203634738567</v>
+        <v>18.412036347385669</v>
       </c>
       <c r="D21">
-        <v>37.20266412940057</v>
+        <v>37.202664129400567</v>
       </c>
       <c r="E21">
         <v>29.62962962962963</v>
       </c>
       <c r="F21">
-        <v>34.61599116858539</v>
+        <v>34.615991168585388</v>
       </c>
       <c r="G21">
-        <v>19.73650874081581</v>
+        <v>19.736508740815811</v>
       </c>
       <c r="H21">
         <v>100</v>
       </c>
       <c r="I21">
-        <v>4.857503152585119</v>
+        <v>4.8575031525851191</v>
       </c>
       <c r="J21">
-        <v>21.0966157086373</v>
+        <v>21.096615708637302</v>
       </c>
       <c r="K21">
-        <v>33.09919122543758</v>
+        <v>33.099191225437579</v>
       </c>
       <c r="L21">
-        <v>26.1948339269204</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>26.194833926920399</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22">
-        <v>29.99999999999999</v>
+        <v>29.999999999999989</v>
       </c>
       <c r="C22">
         <v>21.28705496797259</v>
       </c>
       <c r="D22">
-        <v>35.07136060894386</v>
+        <v>35.071360608943863</v>
       </c>
       <c r="E22">
-        <v>62.91704928068565</v>
+        <v>62.917049280685653</v>
       </c>
       <c r="F22">
         <v>27.62971140198707</v>
       </c>
       <c r="G22">
-        <v>23.94223460856347</v>
+        <v>23.942234608563471</v>
       </c>
       <c r="H22">
         <v>100</v>
@@ -1208,30 +1244,30 @@
         <v>15.78511701373832</v>
       </c>
       <c r="K22">
-        <v>35.55661967357987</v>
+        <v>35.556619673579867</v>
       </c>
       <c r="L22">
-        <v>26.59013086014252</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>26.590130860142519</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23">
-        <v>48.19620253164557</v>
+        <v>48.196202531645568</v>
       </c>
       <c r="C23">
         <v>28.45225681513481</v>
       </c>
       <c r="D23">
-        <v>55.64224548049476</v>
+        <v>55.642245480494758</v>
       </c>
       <c r="E23">
-        <v>47.84205693296603</v>
+        <v>47.842056932966031</v>
       </c>
       <c r="F23">
-        <v>29.80602428639016</v>
+        <v>29.806024286390159</v>
       </c>
       <c r="G23">
         <v>15.50544717506968</v>
@@ -1240,16 +1276,16 @@
         <v>100</v>
       </c>
       <c r="I23">
-        <v>21.47793190416141</v>
+        <v>21.477931904161409</v>
       </c>
       <c r="J23">
-        <v>20.07431976209777</v>
+        <v>20.074319762097769</v>
       </c>
       <c r="K23">
-        <v>40.77738720977337</v>
+        <v>40.777387209773373</v>
       </c>
       <c r="L23">
-        <v>35.25482159956147</v>
+        <v>35.254821599561467</v>
       </c>
     </row>
   </sheetData>
